--- a/virtual-physics-lab/app/dl/VJC_Q2c_hysteresis_dataset.xlsx
+++ b/virtual-physics-lab/app/dl/VJC_Q2c_hysteresis_dataset.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -95,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +106,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,12 +232,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Suggested solution'!$D$6:$D$66</f>
+              <f>'Suggested solution'!$D$6:$D$67</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Suggested solution'!$C$6:$C$66</f>
+              <f>'Suggested solution'!$C$6:$C$67</f>
             </numRef>
           </yVal>
         </ser>
@@ -618,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -682,14 +685,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -697,14 +700,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.091</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>0.109</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -712,14 +715,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.096</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>0.222</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -727,14 +730,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.101</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>0.335</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -742,14 +745,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.106</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>0.447</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -757,14 +760,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.111</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -772,14 +775,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.116</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -787,14 +790,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.121</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -802,14 +805,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>0.126</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>0.931</v>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -817,14 +820,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>0.131</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>1.064</v>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -832,14 +835,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>0.136</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>1.213</v>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -847,14 +850,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.141</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>1.345</v>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -862,14 +865,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>0.146</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>1.496</v>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -877,14 +880,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>0.151</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>1.644</v>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -892,14 +895,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.156</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="6" t="n">
         <v>1.791</v>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -907,14 +910,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>0.161</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>1.976</v>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -922,14 +925,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>0.166</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="6" t="n">
         <v>2.157</v>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -937,14 +940,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>0.171</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <v>2.355</v>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -952,14 +955,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>0.176</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <v>2.524</v>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -967,14 +970,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>0.181</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <v>2.737</v>
       </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -982,14 +985,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>0.186</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <v>2.962</v>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -997,14 +1000,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>0.191</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <v>3.144</v>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1012,14 +1015,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>0.196</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="6" t="n">
         <v>3.414</v>
       </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1027,14 +1030,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>0.201</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>3.628</v>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1042,14 +1045,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>0.206</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <v>3.885</v>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1057,14 +1060,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>0.211</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <v>4.126</v>
       </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1072,14 +1075,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>0.216</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="6" t="n">
         <v>4.42</v>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1087,14 +1090,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>0.221</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>4.667</v>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1102,14 +1105,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>0.226</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="6" t="n">
         <v>4.985</v>
       </c>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1117,14 +1120,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>0.231</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="6" t="n">
         <v>5.27</v>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1132,14 +1135,14 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>0.236</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>5.55</v>
       </c>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1147,14 +1150,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>5.062</v>
-      </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
+      <c r="B37" s="6" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1162,14 +1165,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>4.549</v>
-      </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
+      <c r="B38" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>5.062</v>
+      </c>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1177,14 +1180,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>4.108</v>
-      </c>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
+      <c r="B39" s="6" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1192,14 +1195,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>3.736</v>
-      </c>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
+      <c r="B40" s="6" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>4.108</v>
+      </c>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1207,14 +1210,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>3.375</v>
-      </c>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
+      <c r="B41" s="6" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>3.736</v>
+      </c>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1222,14 +1225,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>3.021</v>
-      </c>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
+      <c r="B42" s="6" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1237,14 +1240,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
+      <c r="B43" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1252,14 +1255,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>2.469</v>
-      </c>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
+      <c r="B44" s="6" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -1267,14 +1270,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
+      <c r="B45" s="6" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1282,14 +1285,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>2.035</v>
-      </c>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
+      <c r="B46" s="6" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -1297,14 +1300,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>1.822</v>
-      </c>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
+      <c r="B47" s="6" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -1312,14 +1315,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>1.636</v>
-      </c>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
+      <c r="B48" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -1327,14 +1330,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>1.483</v>
-      </c>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
+      <c r="B49" s="6" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -1342,14 +1345,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>1.337</v>
-      </c>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
+      <c r="B50" s="6" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -1357,14 +1360,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>1.191</v>
-      </c>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
+      <c r="B51" s="6" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -1372,14 +1375,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
+      <c r="B52" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -1387,14 +1390,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
+      <c r="B53" s="6" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -1402,14 +1405,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
+      <c r="B54" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -1417,14 +1420,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
+      <c r="B55" s="6" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -1432,14 +1435,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
+      <c r="B56" s="6" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -1447,14 +1450,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
+      <c r="B57" s="6" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -1462,14 +1465,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
+      <c r="B58" s="6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -1477,14 +1480,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
+      <c r="B59" s="6" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -1492,14 +1495,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
+      <c r="B60" s="6" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -1507,14 +1510,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
+      <c r="B61" s="6" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -1522,14 +1525,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
+      <c r="B62" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -1537,14 +1540,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
+      <c r="B63" s="6" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -1552,14 +1555,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
+      <c r="B64" s="6" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -1567,14 +1570,14 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
+      <c r="B65" s="6" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -1582,14 +1585,29 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>unloading</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1602,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1677,17 +1695,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>B6-0.086</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>IF(A7=A6,0.5*(C6+C7)*(D7-D6),"")</f>
         <v/>
       </c>
@@ -1696,8 +1714,8 @@
           <t>area under loading (Σ strips, loading rows)</t>
         </is>
       </c>
-      <c r="H6" s="7">
-        <f>SUMIF(A6:A66,"loading",E6:E66)</f>
+      <c r="H6" s="8">
+        <f>SUMIF(A6:A67,"loading",E6:E67)</f>
         <v/>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1712,17 +1730,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.091</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>0.109</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>B7-0.086</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>IF(A8=A7,0.5*(C7+C8)*(D8-D7),"")</f>
         <v/>
       </c>
@@ -1731,8 +1749,8 @@
           <t>area under unloading (−Σ strips, unloading rows)</t>
         </is>
       </c>
-      <c r="H7" s="7">
-        <f>-SUMIF(A6:A66,"unloading",E6:E66)</f>
+      <c r="H7" s="8">
+        <f>-SUMIF(A6:A67,"unloading",E6:E67)</f>
         <v/>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1747,17 +1765,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.096</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>0.222</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>B8-0.086</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>IF(A9=A8,0.5*(C8+C9)*(D9-D8),"")</f>
         <v/>
       </c>
@@ -1766,8 +1784,8 @@
           <t>energy lost = difference</t>
         </is>
       </c>
-      <c r="H8" s="7">
-        <f>SUMIF(A6:A66,"loading",E6:E66)+SUMIF(A6:A66,"unloading",E6:E66)</f>
+      <c r="H8" s="8">
+        <f>SUMIF(A6:A67,"loading",E6:E67)+SUMIF(A6:A67,"unloading",E6:E67)</f>
         <v/>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1782,17 +1800,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.101</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>0.335</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>B9-0.086</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>IF(A10=A9,0.5*(C9+C10)*(D10-D9),"")</f>
         <v/>
       </c>
@@ -1803,21 +1821,21 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.106</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>0.447</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>B10-0.086</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>IF(A11=A10,0.5*(C10+C11)*(D11-D10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>The unloading strips come out negative (e decreasing), so adding the two sums gives the loop area.</t>
         </is>
@@ -1829,17 +1847,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.111</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>B11-0.086</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>IF(A12=A11,0.5*(C11+C12)*(D12-D11),"")</f>
         <v/>
       </c>
@@ -1850,17 +1868,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.116</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>B12-0.086</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>IF(A13=A12,0.5*(C12+C13)*(D13-D12),"")</f>
         <v/>
       </c>
@@ -1871,17 +1889,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.121</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <f>B13-0.086</f>
         <v/>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <f>IF(A14=A13,0.5*(C13+C14)*(D14-D13),"")</f>
         <v/>
       </c>
@@ -1892,17 +1910,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>0.126</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>0.931</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <f>B14-0.086</f>
         <v/>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>IF(A15=A14,0.5*(C14+C15)*(D15-D14),"")</f>
         <v/>
       </c>
@@ -1913,17 +1931,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>0.131</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>1.064</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <f>B15-0.086</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <f>IF(A16=A15,0.5*(C15+C16)*(D16-D15),"")</f>
         <v/>
       </c>
@@ -1934,17 +1952,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>0.136</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>1.213</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <f>B16-0.086</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <f>IF(A17=A16,0.5*(C16+C17)*(D17-D16),"")</f>
         <v/>
       </c>
@@ -1955,17 +1973,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.141</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>1.345</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <f>B17-0.086</f>
         <v/>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>IF(A18=A17,0.5*(C17+C18)*(D18-D17),"")</f>
         <v/>
       </c>
@@ -1976,17 +1994,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>0.146</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>1.496</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <f>B18-0.086</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <f>IF(A19=A18,0.5*(C18+C19)*(D19-D18),"")</f>
         <v/>
       </c>
@@ -1997,17 +2015,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>0.151</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>1.644</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <f>B19-0.086</f>
         <v/>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <f>IF(A20=A19,0.5*(C19+C20)*(D20-D19),"")</f>
         <v/>
       </c>
@@ -2018,17 +2036,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.156</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="6" t="n">
         <v>1.791</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <f>B20-0.086</f>
         <v/>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <f>IF(A21=A20,0.5*(C20+C21)*(D21-D20),"")</f>
         <v/>
       </c>
@@ -2039,17 +2057,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>0.161</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>1.976</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <f>B21-0.086</f>
         <v/>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <f>IF(A22=A21,0.5*(C21+C22)*(D22-D21),"")</f>
         <v/>
       </c>
@@ -2060,17 +2078,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>0.166</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="6" t="n">
         <v>2.157</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <f>B22-0.086</f>
         <v/>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <f>IF(A23=A22,0.5*(C22+C23)*(D23-D22),"")</f>
         <v/>
       </c>
@@ -2081,17 +2099,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>0.171</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <v>2.355</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <f>B23-0.086</f>
         <v/>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <f>IF(A24=A23,0.5*(C23+C24)*(D24-D23),"")</f>
         <v/>
       </c>
@@ -2102,17 +2120,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>0.176</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <v>2.524</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <f>B24-0.086</f>
         <v/>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <f>IF(A25=A24,0.5*(C24+C25)*(D25-D24),"")</f>
         <v/>
       </c>
@@ -2123,17 +2141,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>0.181</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <v>2.737</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <f>B25-0.086</f>
         <v/>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <f>IF(A26=A25,0.5*(C25+C26)*(D26-D25),"")</f>
         <v/>
       </c>
@@ -2144,17 +2162,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>0.186</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <v>2.962</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <f>B26-0.086</f>
         <v/>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <f>IF(A27=A26,0.5*(C26+C27)*(D27-D26),"")</f>
         <v/>
       </c>
@@ -2165,17 +2183,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>0.191</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <v>3.144</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <f>B27-0.086</f>
         <v/>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <f>IF(A28=A27,0.5*(C27+C28)*(D28-D27),"")</f>
         <v/>
       </c>
@@ -2186,17 +2204,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>0.196</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="6" t="n">
         <v>3.414</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <f>B28-0.086</f>
         <v/>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <f>IF(A29=A28,0.5*(C28+C29)*(D29-D28),"")</f>
         <v/>
       </c>
@@ -2207,17 +2225,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>0.201</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>3.628</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <f>B29-0.086</f>
         <v/>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <f>IF(A30=A29,0.5*(C29+C30)*(D30-D29),"")</f>
         <v/>
       </c>
@@ -2228,17 +2246,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>0.206</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <v>3.885</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <f>B30-0.086</f>
         <v/>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <f>IF(A31=A30,0.5*(C30+C31)*(D31-D30),"")</f>
         <v/>
       </c>
@@ -2249,17 +2267,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>0.211</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <v>4.126</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <f>B31-0.086</f>
         <v/>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <f>IF(A32=A31,0.5*(C31+C32)*(D32-D31),"")</f>
         <v/>
       </c>
@@ -2270,17 +2288,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>0.216</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="6" t="n">
         <v>4.42</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <f>B32-0.086</f>
         <v/>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <f>IF(A33=A32,0.5*(C32+C33)*(D33-D32),"")</f>
         <v/>
       </c>
@@ -2291,17 +2309,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>0.221</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>4.667</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <f>B33-0.086</f>
         <v/>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <f>IF(A34=A33,0.5*(C33+C34)*(D34-D33),"")</f>
         <v/>
       </c>
@@ -2312,17 +2330,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>0.226</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="6" t="n">
         <v>4.985</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <f>B34-0.086</f>
         <v/>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <f>IF(A35=A34,0.5*(C34+C35)*(D35-D34),"")</f>
         <v/>
       </c>
@@ -2333,17 +2351,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>0.231</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="6" t="n">
         <v>5.27</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="8">
         <f>B35-0.086</f>
         <v/>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="8">
         <f>IF(A36=A35,0.5*(C35+C36)*(D36-D35),"")</f>
         <v/>
       </c>
@@ -2354,17 +2372,17 @@
           <t>loading</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>0.236</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>5.55</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="8">
         <f>B36-0.086</f>
         <v/>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="8">
         <f>IF(A37=A36,0.5*(C36+C37)*(D37-D36),"")</f>
         <v/>
       </c>
@@ -2375,17 +2393,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>5.062</v>
-      </c>
-      <c r="D37" s="7">
+      <c r="B37" s="6" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D37" s="8">
         <f>B37-0.086</f>
         <v/>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="8">
         <f>IF(A38=A37,0.5*(C37+C38)*(D38-D37),"")</f>
         <v/>
       </c>
@@ -2396,17 +2414,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>4.549</v>
-      </c>
-      <c r="D38" s="7">
+      <c r="B38" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>5.062</v>
+      </c>
+      <c r="D38" s="8">
         <f>B38-0.086</f>
         <v/>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="8">
         <f>IF(A39=A38,0.5*(C38+C39)*(D39-D38),"")</f>
         <v/>
       </c>
@@ -2417,17 +2435,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>4.108</v>
-      </c>
-      <c r="D39" s="7">
+      <c r="B39" s="6" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="D39" s="8">
         <f>B39-0.086</f>
         <v/>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="8">
         <f>IF(A40=A39,0.5*(C39+C40)*(D40-D39),"")</f>
         <v/>
       </c>
@@ -2438,17 +2456,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>3.736</v>
-      </c>
-      <c r="D40" s="7">
+      <c r="B40" s="6" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>4.108</v>
+      </c>
+      <c r="D40" s="8">
         <f>B40-0.086</f>
         <v/>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="8">
         <f>IF(A41=A40,0.5*(C40+C41)*(D41-D40),"")</f>
         <v/>
       </c>
@@ -2459,17 +2477,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>3.375</v>
-      </c>
-      <c r="D41" s="7">
+      <c r="B41" s="6" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>3.736</v>
+      </c>
+      <c r="D41" s="8">
         <f>B41-0.086</f>
         <v/>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="8">
         <f>IF(A42=A41,0.5*(C41+C42)*(D42-D41),"")</f>
         <v/>
       </c>
@@ -2480,17 +2498,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>3.021</v>
-      </c>
-      <c r="D42" s="7">
+      <c r="B42" s="6" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="D42" s="8">
         <f>B42-0.086</f>
         <v/>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="8">
         <f>IF(A43=A42,0.5*(C42+C43)*(D43-D42),"")</f>
         <v/>
       </c>
@@ -2501,17 +2519,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="D43" s="7">
+      <c r="B43" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="D43" s="8">
         <f>B43-0.086</f>
         <v/>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="8">
         <f>IF(A44=A43,0.5*(C43+C44)*(D44-D43),"")</f>
         <v/>
       </c>
@@ -2522,17 +2540,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>2.469</v>
-      </c>
-      <c r="D44" s="7">
+      <c r="B44" s="6" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="D44" s="8">
         <f>B44-0.086</f>
         <v/>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="8">
         <f>IF(A45=A44,0.5*(C44+C45)*(D45-D44),"")</f>
         <v/>
       </c>
@@ -2543,17 +2561,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="D45" s="7">
+      <c r="B45" s="6" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="D45" s="8">
         <f>B45-0.086</f>
         <v/>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="8">
         <f>IF(A46=A45,0.5*(C45+C46)*(D46-D45),"")</f>
         <v/>
       </c>
@@ -2564,17 +2582,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>2.035</v>
-      </c>
-      <c r="D46" s="7">
+      <c r="B46" s="6" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D46" s="8">
         <f>B46-0.086</f>
         <v/>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="8">
         <f>IF(A47=A46,0.5*(C46+C47)*(D47-D46),"")</f>
         <v/>
       </c>
@@ -2585,17 +2603,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>1.822</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="B47" s="6" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="D47" s="8">
         <f>B47-0.086</f>
         <v/>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="8">
         <f>IF(A48=A47,0.5*(C47+C48)*(D48-D47),"")</f>
         <v/>
       </c>
@@ -2606,17 +2624,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>1.636</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="B48" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="D48" s="8">
         <f>B48-0.086</f>
         <v/>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="8">
         <f>IF(A49=A48,0.5*(C48+C49)*(D49-D48),"")</f>
         <v/>
       </c>
@@ -2627,17 +2645,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>1.483</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="B49" s="6" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="D49" s="8">
         <f>B49-0.086</f>
         <v/>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="8">
         <f>IF(A50=A49,0.5*(C49+C50)*(D50-D49),"")</f>
         <v/>
       </c>
@@ -2648,17 +2666,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>1.337</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="B50" s="6" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="D50" s="8">
         <f>B50-0.086</f>
         <v/>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="8">
         <f>IF(A51=A50,0.5*(C50+C51)*(D51-D50),"")</f>
         <v/>
       </c>
@@ -2669,17 +2687,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>1.191</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="B51" s="6" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="D51" s="8">
         <f>B51-0.086</f>
         <v/>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="8">
         <f>IF(A52=A51,0.5*(C51+C52)*(D52-D51),"")</f>
         <v/>
       </c>
@@ -2690,17 +2708,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="B52" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="D52" s="8">
         <f>B52-0.086</f>
         <v/>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="8">
         <f>IF(A53=A52,0.5*(C52+C53)*(D53-D52),"")</f>
         <v/>
       </c>
@@ -2711,17 +2729,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="B53" s="6" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="D53" s="8">
         <f>B53-0.086</f>
         <v/>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="8">
         <f>IF(A54=A53,0.5*(C53+C54)*(D54-D53),"")</f>
         <v/>
       </c>
@@ -2732,17 +2750,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="B54" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="D54" s="8">
         <f>B54-0.086</f>
         <v/>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="8">
         <f>IF(A55=A54,0.5*(C54+C55)*(D55-D54),"")</f>
         <v/>
       </c>
@@ -2753,17 +2771,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="B55" s="6" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="D55" s="8">
         <f>B55-0.086</f>
         <v/>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="8">
         <f>IF(A56=A55,0.5*(C55+C56)*(D56-D55),"")</f>
         <v/>
       </c>
@@ -2774,17 +2792,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="D56" s="7">
+      <c r="B56" s="6" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="D56" s="8">
         <f>B56-0.086</f>
         <v/>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="8">
         <f>IF(A57=A56,0.5*(C56+C57)*(D57-D56),"")</f>
         <v/>
       </c>
@@ -2795,17 +2813,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="D57" s="7">
+      <c r="B57" s="6" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="D57" s="8">
         <f>B57-0.086</f>
         <v/>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="8">
         <f>IF(A58=A57,0.5*(C57+C58)*(D58-D57),"")</f>
         <v/>
       </c>
@@ -2816,17 +2834,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D58" s="7">
+      <c r="B58" s="6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="D58" s="8">
         <f>B58-0.086</f>
         <v/>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="8">
         <f>IF(A59=A58,0.5*(C58+C59)*(D59-D58),"")</f>
         <v/>
       </c>
@@ -2837,17 +2855,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="D59" s="7">
+      <c r="B59" s="6" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D59" s="8">
         <f>B59-0.086</f>
         <v/>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="8">
         <f>IF(A60=A59,0.5*(C59+C60)*(D60-D59),"")</f>
         <v/>
       </c>
@@ -2858,17 +2876,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="D60" s="7">
+      <c r="B60" s="6" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="D60" s="8">
         <f>B60-0.086</f>
         <v/>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="8">
         <f>IF(A61=A60,0.5*(C60+C61)*(D61-D60),"")</f>
         <v/>
       </c>
@@ -2879,17 +2897,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="D61" s="7">
+      <c r="B61" s="6" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="D61" s="8">
         <f>B61-0.086</f>
         <v/>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="8">
         <f>IF(A62=A61,0.5*(C61+C62)*(D62-D61),"")</f>
         <v/>
       </c>
@@ -2900,17 +2918,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="D62" s="7">
+      <c r="B62" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="D62" s="8">
         <f>B62-0.086</f>
         <v/>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="8">
         <f>IF(A63=A62,0.5*(C62+C63)*(D63-D62),"")</f>
         <v/>
       </c>
@@ -2921,17 +2939,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="B63" s="6" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="D63" s="8">
         <f>B63-0.086</f>
         <v/>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="8">
         <f>IF(A64=A63,0.5*(C63+C64)*(D64-D63),"")</f>
         <v/>
       </c>
@@ -2942,17 +2960,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D64" s="7">
+      <c r="B64" s="6" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="D64" s="8">
         <f>B64-0.086</f>
         <v/>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="8">
         <f>IF(A65=A64,0.5*(C64+C65)*(D65-D64),"")</f>
         <v/>
       </c>
@@ -2963,17 +2981,17 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="B65" s="6" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="D65" s="8">
         <f>B65-0.086</f>
         <v/>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="8">
         <f>IF(A66=A65,0.5*(C65+C66)*(D66-D65),"")</f>
         <v/>
       </c>
@@ -2984,18 +3002,39 @@
           <t>unloading</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="D66" s="8">
+        <f>B66-0.086</f>
+        <v/>
+      </c>
+      <c r="E66" s="8">
+        <f>IF(A67=A66,0.5*(C66+C67)*(D67-D66),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>unloading</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="7">
-        <f>B66-0.086</f>
-        <v/>
-      </c>
-      <c r="E66" s="7">
-        <f>IF(A67=A66,0.5*(C66+C67)*(D67-D66),"")</f>
+      <c r="D67" s="8">
+        <f>B67-0.086</f>
+        <v/>
+      </c>
+      <c r="E67" s="8">
+        <f>IF(A68=A67,0.5*(C67+C68)*(D68-D67),"")</f>
         <v/>
       </c>
     </row>
